--- a/Extraction_Tool/NCAA_Fixtures_Final.xlsx
+++ b/Extraction_Tool/NCAA_Fixtures_Final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="299">
   <si>
     <t>Away Team</t>
   </si>
@@ -43,697 +43,676 @@
     <t>Date &amp; Time (Berlin)</t>
   </si>
   <si>
-    <t>George Washington</t>
-  </si>
-  <si>
-    <t>George Mason</t>
-  </si>
-  <si>
-    <t>Dayton</t>
-  </si>
-  <si>
-    <t>Davidson</t>
-  </si>
-  <si>
-    <t>American University</t>
-  </si>
-  <si>
-    <t>Bucknell</t>
-  </si>
-  <si>
-    <t>Navy</t>
-  </si>
-  <si>
-    <t>Youngstown State</t>
-  </si>
-  <si>
-    <t>Central Michigan</t>
-  </si>
-  <si>
-    <t>South Carolina Upstate</t>
-  </si>
-  <si>
-    <t>Northern Kentucky</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Arizona State</t>
-  </si>
-  <si>
-    <t>La Salle</t>
+    <t>Swarthmore</t>
+  </si>
+  <si>
+    <t>Barton</t>
+  </si>
+  <si>
+    <t>SUNY Morrisville</t>
+  </si>
+  <si>
+    <t>Sacred Heart</t>
+  </si>
+  <si>
+    <t>Central Connecticut</t>
+  </si>
+  <si>
+    <t>Valparaiso</t>
+  </si>
+  <si>
+    <t>Florida A&amp;M</t>
+  </si>
+  <si>
+    <t>Green Bay</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Clarke</t>
+  </si>
+  <si>
+    <t>Judson</t>
+  </si>
+  <si>
+    <t>Jacksonville</t>
+  </si>
+  <si>
+    <t>Illinois Springfield</t>
+  </si>
+  <si>
+    <t>Eastern Illinois</t>
+  </si>
+  <si>
+    <t>Florida Gulf Coast</t>
+  </si>
+  <si>
+    <t>Xavier (LA)</t>
+  </si>
+  <si>
+    <t>West Florida</t>
+  </si>
+  <si>
+    <t>Saint Peter's</t>
+  </si>
+  <si>
+    <t>Evansville</t>
+  </si>
+  <si>
+    <t>Stonehill</t>
+  </si>
+  <si>
+    <t>Mercyhurst</t>
+  </si>
+  <si>
+    <t>Oral Roberts</t>
+  </si>
+  <si>
+    <t>Incarnate Word</t>
+  </si>
+  <si>
+    <t>Sacramento State</t>
+  </si>
+  <si>
+    <t>Mississippi Valley State</t>
+  </si>
+  <si>
+    <t>Bradley</t>
+  </si>
+  <si>
+    <t>North Alabama</t>
+  </si>
+  <si>
+    <t>Le Moyne</t>
+  </si>
+  <si>
+    <t>Omaha</t>
+  </si>
+  <si>
+    <t>Westminster (UT)</t>
+  </si>
+  <si>
+    <t>Park University Gilbert</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Eastern Washington</t>
+  </si>
+  <si>
+    <t>Wright State</t>
+  </si>
+  <si>
+    <t>Occidental</t>
+  </si>
+  <si>
+    <t>UC Santa Cruz</t>
+  </si>
+  <si>
+    <t>Montana Western</t>
+  </si>
+  <si>
+    <t>La Sierra</t>
+  </si>
+  <si>
+    <t>Idaho State</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>LeTourneau</t>
+  </si>
+  <si>
+    <t>Wingate</t>
+  </si>
+  <si>
+    <t>Clinton</t>
+  </si>
+  <si>
+    <t>Erskine</t>
+  </si>
+  <si>
+    <t>Montreat</t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>UNC Wilmington</t>
+  </si>
+  <si>
+    <t>Colgate</t>
+  </si>
+  <si>
+    <t>Syracuse</t>
+  </si>
+  <si>
+    <t>VCU</t>
+  </si>
+  <si>
+    <t>Michigan State</t>
+  </si>
+  <si>
+    <t>UCF</t>
+  </si>
+  <si>
+    <t>Duke</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Western Illinois</t>
+  </si>
+  <si>
+    <t>SIU Edwardsville</t>
+  </si>
+  <si>
+    <t>Florida International</t>
+  </si>
+  <si>
+    <t>Southern Illinois</t>
+  </si>
+  <si>
+    <t>Drake</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>East Tennessee State</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
   </si>
   <si>
     <t>DePaul</t>
   </si>
   <si>
-    <t>Winthrop</t>
-  </si>
-  <si>
-    <t>Presbyterian</t>
-  </si>
-  <si>
-    <t>Longwood</t>
-  </si>
-  <si>
-    <t>Lehigh</t>
-  </si>
-  <si>
-    <t>Cleveland State</t>
-  </si>
-  <si>
-    <t>Western Michigan</t>
-  </si>
-  <si>
-    <t>Buffalo</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Coastal Carolina</t>
-  </si>
-  <si>
-    <t>Nebraska</t>
+    <t>Providence</t>
+  </si>
+  <si>
+    <t>Seton Hall</t>
+  </si>
+  <si>
+    <t>TCU</t>
+  </si>
+  <si>
+    <t>Tulsa</t>
+  </si>
+  <si>
+    <t>UT Arlington</t>
+  </si>
+  <si>
+    <t>Marquette</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Mississippi State</t>
+  </si>
+  <si>
+    <t>SMU</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Weber State</t>
+  </si>
+  <si>
+    <t>Utah Valley</t>
+  </si>
+  <si>
+    <t>Northwestern</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Loyola Chicago</t>
+  </si>
+  <si>
+    <t>UC Riverside</t>
+  </si>
+  <si>
+    <t>UC Santa Barbara</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Cal State Northridge</t>
+  </si>
+  <si>
+    <t>BYU</t>
+  </si>
+  <si>
+    <t>Stephen F. Austin</t>
+  </si>
+  <si>
+    <t>Houston Christian</t>
+  </si>
+  <si>
+    <t>High Point</t>
+  </si>
+  <si>
+    <t>UNC Asheville</t>
+  </si>
+  <si>
+    <t>Furman</t>
+  </si>
+  <si>
+    <t>App State</t>
+  </si>
+  <si>
+    <t>Norfolk State</t>
+  </si>
+  <si>
+    <t>The Palestra</t>
+  </si>
+  <si>
+    <t>Trask Coliseum</t>
+  </si>
+  <si>
+    <t>Cotterell Court</t>
+  </si>
+  <si>
+    <t>JMA Wireless Dome</t>
+  </si>
+  <si>
+    <t>Siegel Center</t>
+  </si>
+  <si>
+    <t>Breslin Center</t>
+  </si>
+  <si>
+    <t>Addition Financial Arena</t>
+  </si>
+  <si>
+    <t>Cameron Indoor Stadium</t>
+  </si>
+  <si>
+    <t>Hope Coliseum</t>
+  </si>
+  <si>
+    <t>Western Hall</t>
+  </si>
+  <si>
+    <t>First Community Arena</t>
+  </si>
+  <si>
+    <t>Ocean Bank Convocation Center</t>
+  </si>
+  <si>
+    <t>Banterra Center</t>
+  </si>
+  <si>
+    <t>Knapp Center</t>
+  </si>
+  <si>
+    <t>Simon Skjodt Assembly Hall</t>
+  </si>
+  <si>
+    <t>Cajundome</t>
+  </si>
+  <si>
+    <t>Brooks Gymnasium</t>
+  </si>
+  <si>
+    <t>Petersen Events Center</t>
+  </si>
+  <si>
+    <t>Wintrust Arena</t>
+  </si>
+  <si>
+    <t>Alumni Hall (RI)</t>
+  </si>
+  <si>
+    <t>Walsh Gymnasium</t>
+  </si>
+  <si>
+    <t>Schollmaier Arena</t>
+  </si>
+  <si>
+    <t>Reynolds Center</t>
+  </si>
+  <si>
+    <t>College Park Center</t>
+  </si>
+  <si>
+    <t>Al McGuire Center</t>
+  </si>
+  <si>
+    <t>Kohl Center</t>
+  </si>
+  <si>
+    <t>Humphrey Coliseum</t>
+  </si>
+  <si>
+    <t>Moody Coliseum (Dallas)</t>
+  </si>
+  <si>
+    <t>Allen Fieldhouse</t>
+  </si>
+  <si>
+    <t>Dee Events Center</t>
+  </si>
+  <si>
+    <t>UCCU Center</t>
+  </si>
+  <si>
+    <t>Welsh-Ryan Arena</t>
+  </si>
+  <si>
+    <t>Jon M. Huntsman Center</t>
+  </si>
+  <si>
+    <t>Gentile Arena</t>
+  </si>
+  <si>
+    <t>SRC Arena</t>
+  </si>
+  <si>
+    <t>The Thunderdome</t>
+  </si>
+  <si>
+    <t>Dahlberg Arena</t>
+  </si>
+  <si>
+    <t>Premier America Credit Union Arena</t>
+  </si>
+  <si>
+    <t>Marriott Center</t>
+  </si>
+  <si>
+    <t>William R. Johnson Coliseum</t>
+  </si>
+  <si>
+    <t>Sharp Gymnasium</t>
+  </si>
+  <si>
+    <t>Qubein Center</t>
+  </si>
+  <si>
+    <t>Kimmel Arena</t>
+  </si>
+  <si>
+    <t>Timmons Arena</t>
+  </si>
+  <si>
+    <t>Holmes Convocation Center</t>
+  </si>
+  <si>
+    <t>Joseph G. Echols Hall</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Wilmington</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Richmond</t>
+  </si>
+  <si>
+    <t>East Lansing</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>Durham</t>
+  </si>
+  <si>
+    <t>Morgantown</t>
+  </si>
+  <si>
+    <t>Macomb</t>
+  </si>
+  <si>
+    <t>Edwardsville</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>Carbondale</t>
+  </si>
+  <si>
+    <t>Des Moines</t>
+  </si>
+  <si>
+    <t>Bloomington</t>
+  </si>
+  <si>
+    <t>Lafayette</t>
+  </si>
+  <si>
+    <t>Johnson City</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>South Orange</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>Arlington</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Starkville</t>
+  </si>
+  <si>
+    <t>Lawrence</t>
+  </si>
+  <si>
+    <t>Ogden</t>
+  </si>
+  <si>
+    <t>Orem</t>
+  </si>
+  <si>
+    <t>Evanston</t>
+  </si>
+  <si>
+    <t>Salt Lake City</t>
+  </si>
+  <si>
+    <t>Riverside</t>
+  </si>
+  <si>
+    <t>Santa Barbara</t>
+  </si>
+  <si>
+    <t>Missoula</t>
+  </si>
+  <si>
+    <t>Northridge</t>
+  </si>
+  <si>
+    <t>Provo</t>
+  </si>
+  <si>
+    <t>Nacogdoches</t>
   </si>
   <si>
     <t>Houston</t>
   </si>
   <si>
-    <t>Cincinnati</t>
-  </si>
-  <si>
-    <t>West Georgia</t>
-  </si>
-  <si>
-    <t>UCF</t>
-  </si>
-  <si>
-    <t>Marquette</t>
-  </si>
-  <si>
-    <t>Kansas City</t>
-  </si>
-  <si>
-    <t>South Dakota State</t>
-  </si>
-  <si>
-    <t>North Dakota State</t>
-  </si>
-  <si>
-    <t>App State</t>
-  </si>
-  <si>
-    <t>UT Arlington</t>
-  </si>
-  <si>
-    <t>Utah State</t>
-  </si>
-  <si>
-    <t>Grand Canyon</t>
-  </si>
-  <si>
-    <t>Fresno State</t>
-  </si>
-  <si>
-    <t>Texas Tech</t>
-  </si>
-  <si>
-    <t>Penn State</t>
-  </si>
-  <si>
-    <t>Minnesota</t>
-  </si>
-  <si>
-    <t>Air Force</t>
-  </si>
-  <si>
-    <t>Purdue</t>
-  </si>
-  <si>
-    <t>Nevada</t>
-  </si>
-  <si>
-    <t>UMass Lowell</t>
-  </si>
-  <si>
-    <t>Lipscomb</t>
-  </si>
-  <si>
-    <t>Western Illinois</t>
-  </si>
-  <si>
-    <t>VCU</t>
-  </si>
-  <si>
-    <t>St. Bonaventure</t>
-  </si>
-  <si>
-    <t>Duquesne</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Colgate</t>
-  </si>
-  <si>
-    <t>Army</t>
-  </si>
-  <si>
-    <t>Holy Cross</t>
-  </si>
-  <si>
-    <t>Robert Morris</t>
-  </si>
-  <si>
-    <t>Akron</t>
-  </si>
-  <si>
-    <t>UNC Asheville</t>
-  </si>
-  <si>
-    <t>IU Indianapolis</t>
-  </si>
-  <si>
-    <t>Ball State</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Loyola Chicago</t>
-  </si>
-  <si>
-    <t>Butler</t>
-  </si>
-  <si>
-    <t>High Point</t>
-  </si>
-  <si>
-    <t>Gardner-Webb</t>
-  </si>
-  <si>
-    <t>Radford</t>
-  </si>
-  <si>
-    <t>Loyola Maryland</t>
-  </si>
-  <si>
-    <t>Purdue Fort Wayne</t>
-  </si>
-  <si>
-    <t>Northern Illinois</t>
-  </si>
-  <si>
-    <t>Miami (OH)</t>
-  </si>
-  <si>
-    <t>Bowling Green</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t>Wisconsin</t>
-  </si>
-  <si>
-    <t>Kansas State</t>
-  </si>
-  <si>
-    <t>Iowa State</t>
-  </si>
-  <si>
-    <t>Central Arkansas</t>
-  </si>
-  <si>
-    <t>Baylor</t>
-  </si>
-  <si>
-    <t>St. John's</t>
-  </si>
-  <si>
-    <t>Denver</t>
-  </si>
-  <si>
-    <t>North Dakota</t>
-  </si>
-  <si>
-    <t>St. Thomas-Minnesota</t>
-  </si>
-  <si>
-    <t>Texas State</t>
-  </si>
-  <si>
-    <t>Tarleton State</t>
-  </si>
-  <si>
-    <t>Wyoming</t>
-  </si>
-  <si>
-    <t>Colorado State</t>
-  </si>
-  <si>
-    <t>Boise State</t>
-  </si>
-  <si>
-    <t>BYU</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>Oregon</t>
-  </si>
-  <si>
-    <t>UNLV</t>
-  </si>
-  <si>
-    <t>UCLA</t>
-  </si>
-  <si>
-    <t>San José State</t>
-  </si>
-  <si>
-    <t>Vermont</t>
-  </si>
-  <si>
-    <t>Stetson</t>
-  </si>
-  <si>
-    <t>Morehead State</t>
-  </si>
-  <si>
-    <t>Siegel Center</t>
-  </si>
-  <si>
-    <t>Reilly Center</t>
-  </si>
-  <si>
-    <t>UPMC Cooper Fieldhouse</t>
-  </si>
-  <si>
-    <t>Thomas M. Ryan Center</t>
-  </si>
-  <si>
-    <t>Cotterell Court</t>
-  </si>
-  <si>
-    <t>Christl Arena</t>
-  </si>
-  <si>
-    <t>Hart Center</t>
-  </si>
-  <si>
-    <t>UPMC Events Center</t>
-  </si>
-  <si>
-    <t>James A. Rhodes Arena</t>
-  </si>
-  <si>
-    <t>Kimmel Arena</t>
-  </si>
-  <si>
-    <t>The Jungle</t>
-  </si>
-  <si>
-    <t>Worthen Arena</t>
-  </si>
-  <si>
-    <t>WVU Coliseum</t>
-  </si>
-  <si>
-    <t>Gentile Arena</t>
-  </si>
-  <si>
-    <t>Hinkle Fieldhouse</t>
-  </si>
-  <si>
-    <t>Qubein Center</t>
-  </si>
-  <si>
-    <t>Paul Porter Arena</t>
-  </si>
-  <si>
-    <t>The Dedmon Center</t>
-  </si>
-  <si>
-    <t>Reitz Arena</t>
-  </si>
-  <si>
-    <t>Hilliard Gates Sports Center</t>
-  </si>
-  <si>
-    <t>NIU Convocation Center</t>
-  </si>
-  <si>
-    <t>Millett Hall</t>
-  </si>
-  <si>
-    <t>Stroh Center</t>
-  </si>
-  <si>
-    <t>Cajundome</t>
-  </si>
-  <si>
-    <t>Kohl Center</t>
-  </si>
-  <si>
-    <t>Bramlage Coliseum</t>
-  </si>
-  <si>
-    <t>Hilton Coliseum</t>
-  </si>
-  <si>
-    <t>Farris Center</t>
-  </si>
-  <si>
-    <t>Foster Pavilion</t>
-  </si>
-  <si>
-    <t>Carnesecca Arena</t>
-  </si>
-  <si>
-    <t>Hamilton Gymnasium</t>
-  </si>
-  <si>
-    <t>Betty Engelstad Sioux Center</t>
-  </si>
-  <si>
-    <t>Lee &amp; Penny Anderson Arena</t>
-  </si>
-  <si>
-    <t>Strahan Arena at the University Events Center</t>
-  </si>
-  <si>
-    <t>Wisdom Gym</t>
-  </si>
-  <si>
-    <t>Arena-Auditorium</t>
-  </si>
-  <si>
-    <t>Moby Arena</t>
-  </si>
-  <si>
-    <t>ExtraMile Arena</t>
-  </si>
-  <si>
-    <t>Marriott Center</t>
-  </si>
-  <si>
-    <t>Alaska Airlines Arena</t>
-  </si>
-  <si>
-    <t>Matthew Knight Arena</t>
-  </si>
-  <si>
-    <t>Cox Pavilion</t>
-  </si>
-  <si>
-    <t>Pauley Pavilion</t>
-  </si>
-  <si>
-    <t>Provident Credit Union Event Center</t>
-  </si>
-  <si>
-    <t>Patrick Gymnasium</t>
-  </si>
-  <si>
-    <t>Edmunds Center</t>
-  </si>
-  <si>
-    <t>Ellis T. Johnson Arena</t>
-  </si>
-  <si>
-    <t>Richmond</t>
-  </si>
-  <si>
-    <t>Saint Bonaventure</t>
-  </si>
-  <si>
-    <t>Pittsburgh</t>
-  </si>
-  <si>
-    <t>Kingston</t>
-  </si>
-  <si>
-    <t>Hamilton</t>
-  </si>
-  <si>
-    <t>West Point</t>
-  </si>
-  <si>
-    <t>Worcester</t>
-  </si>
-  <si>
-    <t>Moon Township</t>
-  </si>
-  <si>
     <t>Asheville</t>
   </si>
   <si>
-    <t>Indianapolis</t>
-  </si>
-  <si>
-    <t>Muncie</t>
-  </si>
-  <si>
-    <t>Morgantown</t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>Boiling Springs</t>
-  </si>
-  <si>
-    <t>Baltimore</t>
-  </si>
-  <si>
-    <t>Fort Wayne</t>
-  </si>
-  <si>
-    <t>Dekalb</t>
-  </si>
-  <si>
-    <t>Oxford</t>
-  </si>
-  <si>
-    <t>Lafayette</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>Manhattan</t>
-  </si>
-  <si>
-    <t>Ames</t>
-  </si>
-  <si>
-    <t>Conway</t>
-  </si>
-  <si>
-    <t>Waco</t>
-  </si>
-  <si>
-    <t>Queens</t>
-  </si>
-  <si>
-    <t>Grand Forks</t>
-  </si>
-  <si>
-    <t>Saint Paul</t>
-  </si>
-  <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
-    <t>Stephenville</t>
-  </si>
-  <si>
-    <t>Laramie</t>
-  </si>
-  <si>
-    <t>Fort Collins</t>
-  </si>
-  <si>
-    <t>Boise</t>
-  </si>
-  <si>
-    <t>Provo</t>
-  </si>
-  <si>
-    <t>Seattle</t>
-  </si>
-  <si>
-    <t>Eugene</t>
-  </si>
-  <si>
-    <t>Las Vegas</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>San Jose</t>
-  </si>
-  <si>
-    <t>Burlington</t>
-  </si>
-  <si>
-    <t>DeLand</t>
-  </si>
-  <si>
-    <t>Morehead</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829089/g-washington-vcu</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829088/george-mason-st-bonaventure</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829087/dayton-duquesne</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829086/davidson-rhode-island</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827869/american-colgate</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823163/bucknell-army</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823072/navy-holy-cross</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401817743/youngstown-st-robert-morris</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401814632/c-michigan-akron</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401820531/sc-upstate-unc-asheville</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401817741/n-kentucky-iu-indy</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401814633/umass-ball-state</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827348/arizona-st-west-virginia</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829090/la-salle-loyola-chicago</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825649/depaul-butler</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823986/winthrop-high-point</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823985/presbyterian-gardner-webb</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823984/longwood-radford</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401823097/lehigh-loyola-md</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401817742/cleveland-st-purdue-fw</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401814635/w-michigan-n-illinois</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401814634/buffalo-miami-oh</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401813209/ohio-bowling-green</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401808772/coastal-louisiana</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825286/nebraska-wisconsin</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827347/houston-kansas-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827346/cincinnati-iowa-state</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401807805/west-georgia-c-arkansas</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827344/ucf-baylor</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825650/marquette-st-johns</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401818466/kansas-city-denver</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401818465/s-dakota-st-north-dakota</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401818464/n-dakota-st-st-thomas-mn</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401808740/app-state-texas-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401805110/ut-arlington-tarleton-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829766/utah-state-wyoming</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829608/grand-canyon-colorado-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829570/fresno-st-boise-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827345/texas-tech-byu</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825287/penn-state-washington</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825285/minnesota-oregon</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401827579/air-force-unlv</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401825288/purdue-ucla</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401829586/nevada-san-jose-st</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401812204/umass-lowell-vermont</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401807810/lipscomb-stetson</t>
-  </si>
-  <si>
-    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401806561/w-illinois-morehead-st</t>
-  </si>
-  <si>
-    <t>01/21/2026</t>
-  </si>
-  <si>
-    <t>01/22/2026</t>
+    <t>Greenville</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>Norfolk</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401931546/swarthmore-penn</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401927977/barton-unc-wilmington</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919552/suny-morrisvle-colgate</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918038/sacred-heart-syracuse</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401915782/c-connecticut-vcu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401920013/valparaiso-michigan-st</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919056/florida-am-ucf</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401915906/green-bay-duke</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401907163/rhode-island-west-virginia</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401929319/clarke-w-illinois</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401928011/judson-siue</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401926100/jacksonville-fiu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919984/il-springfield-s-illinois</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919673/e-illinois-drake</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918923/fgcu-indiana</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918666/xavier-la-louisiana</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401913898/west-florida-etsu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401913744/saint-peters-pitt</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401913044/evansville-depaul</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401913034/stonehill-providence</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401913024/mercyhurst-seton-hall</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401917938/oral-roberts-tcu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401923735/incarnate-word-tulsa</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401921597/sacramento-st-ut-arlington</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919074/miss-valley-st-marquette</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918864/bradley-wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918854/north-alabama-mississippi-st</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401915960/le-moyne-smu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401906962/omaha-kansas</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401927017/westminster-ut-weber-st</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401923131/park-u-gilbert-utah-valley</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401921442/milwaukee-northwestern</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918931/e-washington-utah</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401911753/wright-st-loyola-chicago</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401929240/occidental-uc-riverside</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401928371/uc-santa-cruz-santa-barbara</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401926986/mt-western-montana</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401921546/la-sierra-csu-northridge</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401916149/idaho-st-byu</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401925729/dallas-sf-austin</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401923000/letourneau-hou-christian</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401920335/wingate-high-point</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401927052/clinton-unc-asheville</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401929009/erskine-furman</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401918713/montreat-app-state</t>
+  </si>
+  <si>
+    <t>https://www.espn.com/womens-college-basketball/game/_/gameId/401919645/dist-columbia-norfolk-st</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>11/04/2026</t>
   </si>
   <si>
     <t>11:00:00 PM</t>
@@ -751,196 +730,187 @@
     <t>01:00:00 AM</t>
   </si>
   <si>
-    <t>01:30:00 AM</t>
-  </si>
-  <si>
     <t>02:00:00 AM</t>
   </si>
   <si>
-    <t>02:30:00 AM</t>
-  </si>
-  <si>
-    <t>03:00:00 AM</t>
-  </si>
-  <si>
-    <t>04:00:00 PM</t>
+    <t>05:00:00 PM</t>
+  </si>
+  <si>
+    <t>09:30:00 PM</t>
   </si>
   <si>
     <t>10:00:00 PM</t>
   </si>
   <si>
-    <t>VCU v George Washington</t>
-  </si>
-  <si>
-    <t>St. Bonaventure v George Mason</t>
-  </si>
-  <si>
-    <t>Duquesne v Dayton</t>
-  </si>
-  <si>
-    <t>Rhode Island v Davidson</t>
-  </si>
-  <si>
-    <t>Colgate v American University</t>
-  </si>
-  <si>
-    <t>Army v Bucknell</t>
-  </si>
-  <si>
-    <t>Holy Cross v Navy</t>
-  </si>
-  <si>
-    <t>Robert Morris v Youngstown State</t>
-  </si>
-  <si>
-    <t>Akron v Central Michigan</t>
-  </si>
-  <si>
-    <t>UNC Asheville v South Carolina Upstate</t>
-  </si>
-  <si>
-    <t>IU Indianapolis v Northern Kentucky</t>
-  </si>
-  <si>
-    <t>Ball State v Massachusetts</t>
-  </si>
-  <si>
-    <t>West Virginia v Arizona State</t>
-  </si>
-  <si>
-    <t>Loyola Chicago v La Salle</t>
-  </si>
-  <si>
-    <t>Butler v DePaul</t>
-  </si>
-  <si>
-    <t>High Point v Winthrop</t>
-  </si>
-  <si>
-    <t>Gardner-Webb v Presbyterian</t>
-  </si>
-  <si>
-    <t>Radford v Longwood</t>
-  </si>
-  <si>
-    <t>Loyola Maryland v Lehigh</t>
-  </si>
-  <si>
-    <t>Purdue Fort Wayne v Cleveland State</t>
-  </si>
-  <si>
-    <t>Northern Illinois v Western Michigan</t>
-  </si>
-  <si>
-    <t>Miami (OH) v Buffalo</t>
-  </si>
-  <si>
-    <t>Bowling Green v Ohio</t>
-  </si>
-  <si>
-    <t>Louisiana v Coastal Carolina</t>
-  </si>
-  <si>
-    <t>Wisconsin v Nebraska</t>
-  </si>
-  <si>
-    <t>Kansas State v Houston</t>
-  </si>
-  <si>
-    <t>Iowa State v Cincinnati</t>
-  </si>
-  <si>
-    <t>Central Arkansas v West Georgia</t>
-  </si>
-  <si>
-    <t>Baylor v UCF</t>
-  </si>
-  <si>
-    <t>St. John's v Marquette</t>
-  </si>
-  <si>
-    <t>Denver v Kansas City</t>
-  </si>
-  <si>
-    <t>North Dakota v South Dakota State</t>
-  </si>
-  <si>
-    <t>St. Thomas-Minnesota v North Dakota State</t>
-  </si>
-  <si>
-    <t>Texas State v App State</t>
-  </si>
-  <si>
-    <t>Tarleton State v UT Arlington</t>
-  </si>
-  <si>
-    <t>Wyoming v Utah State</t>
-  </si>
-  <si>
-    <t>Colorado State v Grand Canyon</t>
-  </si>
-  <si>
-    <t>Boise State v Fresno State</t>
-  </si>
-  <si>
-    <t>BYU v Texas Tech</t>
-  </si>
-  <si>
-    <t>Washington v Penn State</t>
-  </si>
-  <si>
-    <t>Oregon v Minnesota</t>
-  </si>
-  <si>
-    <t>UNLV v Air Force</t>
-  </si>
-  <si>
-    <t>UCLA v Purdue</t>
-  </si>
-  <si>
-    <t>San José State v Nevada</t>
-  </si>
-  <si>
-    <t>Vermont v UMass Lowell</t>
-  </si>
-  <si>
-    <t>Stetson v Lipscomb</t>
-  </si>
-  <si>
-    <t>Morehead State v Western Illinois</t>
-  </si>
-  <si>
-    <t>2026-01-22 00:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 00:30 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 01:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 01:30 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 02:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 02:30 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 03:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 03:30 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 04:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 17:00 CET</t>
-  </si>
-  <si>
-    <t>2026-01-22 23:00 CET</t>
+    <t>10:30:00 PM</t>
+  </si>
+  <si>
+    <t>Pennsylvania v Swarthmore</t>
+  </si>
+  <si>
+    <t>UNC Wilmington v Barton</t>
+  </si>
+  <si>
+    <t>Colgate v SUNY Morrisville</t>
+  </si>
+  <si>
+    <t>Syracuse v Sacred Heart</t>
+  </si>
+  <si>
+    <t>VCU v Central Connecticut</t>
+  </si>
+  <si>
+    <t>Michigan State v Valparaiso</t>
+  </si>
+  <si>
+    <t>UCF v Florida A&amp;M</t>
+  </si>
+  <si>
+    <t>Duke v Green Bay</t>
+  </si>
+  <si>
+    <t>West Virginia v Rhode Island</t>
+  </si>
+  <si>
+    <t>Western Illinois v Clarke</t>
+  </si>
+  <si>
+    <t>SIU Edwardsville v Judson</t>
+  </si>
+  <si>
+    <t>Florida International v Jacksonville</t>
+  </si>
+  <si>
+    <t>Southern Illinois v Illinois Springfield</t>
+  </si>
+  <si>
+    <t>Drake v Eastern Illinois</t>
+  </si>
+  <si>
+    <t>Indiana v Florida Gulf Coast</t>
+  </si>
+  <si>
+    <t>Louisiana v Xavier (LA)</t>
+  </si>
+  <si>
+    <t>East Tennessee State v West Florida</t>
+  </si>
+  <si>
+    <t>Pittsburgh v Saint Peter's</t>
+  </si>
+  <si>
+    <t>DePaul v Evansville</t>
+  </si>
+  <si>
+    <t>Providence v Stonehill</t>
+  </si>
+  <si>
+    <t>Seton Hall v Mercyhurst</t>
+  </si>
+  <si>
+    <t>TCU v Oral Roberts</t>
+  </si>
+  <si>
+    <t>Tulsa v Incarnate Word</t>
+  </si>
+  <si>
+    <t>UT Arlington v Sacramento State</t>
+  </si>
+  <si>
+    <t>Marquette v Mississippi Valley State</t>
+  </si>
+  <si>
+    <t>Wisconsin v Bradley</t>
+  </si>
+  <si>
+    <t>Mississippi State v North Alabama</t>
+  </si>
+  <si>
+    <t>SMU v Le Moyne</t>
+  </si>
+  <si>
+    <t>Kansas v Omaha</t>
+  </si>
+  <si>
+    <t>Weber State v Westminster (UT)</t>
+  </si>
+  <si>
+    <t>Utah Valley v Park University Gilbert</t>
+  </si>
+  <si>
+    <t>Northwestern v Milwaukee</t>
+  </si>
+  <si>
+    <t>Utah v Eastern Washington</t>
+  </si>
+  <si>
+    <t>Loyola Chicago v Wright State</t>
+  </si>
+  <si>
+    <t>UC Riverside v Occidental</t>
+  </si>
+  <si>
+    <t>UC Santa Barbara v UC Santa Cruz</t>
+  </si>
+  <si>
+    <t>Montana v Montana Western</t>
+  </si>
+  <si>
+    <t>Cal State Northridge v La Sierra</t>
+  </si>
+  <si>
+    <t>BYU v Idaho State</t>
+  </si>
+  <si>
+    <t>Stephen F. Austin v Dallas</t>
+  </si>
+  <si>
+    <t>Houston Christian v LeTourneau</t>
+  </si>
+  <si>
+    <t>High Point v Wingate</t>
+  </si>
+  <si>
+    <t>UNC Asheville v Clinton</t>
+  </si>
+  <si>
+    <t>Furman v Erskine</t>
+  </si>
+  <si>
+    <t>App State v Montreat</t>
+  </si>
+  <si>
+    <t>Norfolk State v District of Columbia</t>
+  </si>
+  <si>
+    <t>2026-11-04 00:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 00:30 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 01:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 01:30 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 02:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 03:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 18:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 22:30 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 23:00 CET</t>
+  </si>
+  <si>
+    <t>2026-11-04 23:30 CET</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1348,28 +1318,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1377,28 +1347,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1406,28 +1376,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F4" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H4" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="I4" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1435,28 +1405,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="I5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1464,28 +1434,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G6" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H6" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1493,28 +1463,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F7" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H7" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I7" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1522,28 +1492,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F8" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G8" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I8" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1551,28 +1521,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F9" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G9" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I9" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1580,28 +1550,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F10" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H10" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="I10" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1609,28 +1579,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G11" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H11" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I11" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1638,28 +1608,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F12" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I12" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1667,28 +1637,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F13" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G13" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H13" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="I13" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1696,28 +1666,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G14" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H14" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I14" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1725,28 +1695,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G15" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H15" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I15" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1754,28 +1724,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F16" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G16" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H16" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I16" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1783,28 +1753,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F17" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G17" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H17" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1812,28 +1782,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F18" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G18" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H18" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I18" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1841,28 +1811,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G19" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H19" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="I19" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1870,28 +1840,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G20" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H20" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="I20" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1899,28 +1869,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F21" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G21" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H21" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I21" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1928,28 +1898,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G22" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H22" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I22" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1957,28 +1927,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G23" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H23" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1986,28 +1956,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F24" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H24" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I24" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2015,28 +1985,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F25" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G25" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H25" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="I25" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2044,28 +2014,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F26" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G26" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H26" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I26" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2073,28 +2043,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F27" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G27" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H27" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I27" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2102,28 +2072,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F28" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G28" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H28" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I28" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2131,28 +2101,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F29" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G29" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H29" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I29" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2160,28 +2130,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F30" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G30" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="H30" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I30" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2189,28 +2159,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F31" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G31" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H31" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="I31" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2218,28 +2188,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F32" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H32" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I32" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2247,28 +2217,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F33" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G33" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H33" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I33" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2276,28 +2246,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F34" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G34" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H34" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="I34" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2305,28 +2275,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F35" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G35" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H35" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="I35" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2334,28 +2304,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F36" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G36" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H36" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I36" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2363,28 +2333,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F37" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G37" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H37" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I37" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2392,28 +2362,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F38" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G38" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H38" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="I38" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2421,28 +2391,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F39" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G39" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="H39" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I39" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2450,28 +2420,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F40" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G40" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="H40" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="I40" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2479,28 +2449,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F41" t="s">
+        <v>232</v>
+      </c>
+      <c r="G41" t="s">
         <v>239</v>
       </c>
-      <c r="G41" t="s">
-        <v>246</v>
-      </c>
       <c r="H41" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I41" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2508,28 +2478,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F42" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" t="s">
         <v>239</v>
       </c>
-      <c r="G42" t="s">
-        <v>246</v>
-      </c>
       <c r="H42" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="I42" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2537,28 +2507,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F43" t="s">
+        <v>232</v>
+      </c>
+      <c r="G43" t="s">
         <v>239</v>
       </c>
-      <c r="G43" t="s">
-        <v>247</v>
-      </c>
       <c r="H43" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="I43" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2566,28 +2536,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F44" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G44" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="H44" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="I44" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2595,28 +2565,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F45" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G45" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="H45" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I45" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2624,28 +2594,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F46" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G46" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H46" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I46" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2653,57 +2623,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F47" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G47" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H47" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="I47" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" t="s">
-        <v>149</v>
-      </c>
-      <c r="D48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F48" t="s">
-        <v>239</v>
-      </c>
-      <c r="G48" t="s">
-        <v>250</v>
-      </c>
-      <c r="H48" t="s">
-        <v>297</v>
-      </c>
-      <c r="I48" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2754,7 +2695,6 @@
     <hyperlink ref="E45" r:id="rId44"/>
     <hyperlink ref="E46" r:id="rId45"/>
     <hyperlink ref="E47" r:id="rId46"/>
-    <hyperlink ref="E48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
